--- a/spreadsheets/03_MAD/COMBINED_MAD/MAD_DATA.xlsx
+++ b/spreadsheets/03_MAD/COMBINED_MAD/MAD_DATA.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -3905,7 +3905,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3967,7 +3967,6 @@
     <xf numFmtId="22" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3983,6 +3982,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -32570,7 +32573,7 @@
       <c r="I457" s="20" t="s">
         <v>940</v>
       </c>
-      <c r="J457" s="23" t="s">
+      <c r="J457" s="5" t="s">
         <v>941</v>
       </c>
       <c r="K457" s="21">
@@ -33314,7 +33317,7 @@
       <c r="I469" s="20" t="s">
         <v>964</v>
       </c>
-      <c r="J469" s="23" t="s">
+      <c r="J469" s="5" t="s">
         <v>965</v>
       </c>
       <c r="K469" s="21">
